--- a/experiments/nrp_sat_scl_exp_results.xlsx
+++ b/experiments/nrp_sat_scl_exp_results.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,30 +447,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>encoding_time_sec</t>
+          <t>total_time_sec</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>solving_time_sec</t>
+          <t>peak_memory_mb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total_time_sec</t>
+          <t>total_clauses</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>peak_memory_mb</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>total_clauses</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>total_variables</t>
         </is>
@@ -495,19 +485,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0112384</v>
+        <v>0.0155321</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00429377</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.0155321</v>
-      </c>
-      <c r="I2" t="n">
         <v>5.7</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -528,19 +512,13 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0112592</v>
+        <v>0.0156504</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00439118</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.0156504</v>
-      </c>
-      <c r="I3" t="n">
         <v>5.7</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -561,19 +539,13 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0114624</v>
+        <v>0.0157593</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00429688</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0157593</v>
-      </c>
-      <c r="I4" t="n">
         <v>5.7</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -594,19 +566,13 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0117934</v>
+        <v>0.0161632</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00436984</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0161632</v>
-      </c>
-      <c r="I5" t="n">
         <v>5.6</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -627,19 +593,13 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0113563</v>
+        <v>0.0157726</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00441622</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.0157726</v>
-      </c>
-      <c r="I6" t="n">
         <v>5.7</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -660,19 +620,13 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0111856</v>
+        <v>0.0154972</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00431165</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.0154972</v>
-      </c>
-      <c r="I7" t="n">
         <v>5.6</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -693,19 +647,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0113704</v>
+        <v>0.0156353</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00426493</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.0156353</v>
-      </c>
-      <c r="I8" t="n">
         <v>5.6</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -726,19 +674,13 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0112725</v>
+        <v>0.0155321</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00425964</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0155321</v>
-      </c>
-      <c r="I9" t="n">
         <v>5.7</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -759,19 +701,13 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0112101</v>
+        <v>0.0154802</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0042701</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.0154802</v>
-      </c>
-      <c r="I10" t="n">
         <v>5.6</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -792,19 +728,13 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0110138</v>
+        <v>0.0152696</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00425581</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.0152696</v>
-      </c>
-      <c r="I11" t="n">
         <v>5.6</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -827,19 +757,13 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01131621</v>
+        <v>0.0156292</v>
       </c>
       <c r="G12" t="n">
-        <v>0.004313002</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.0156292</v>
-      </c>
-      <c r="I12" t="n">
         <v>5.65</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -852,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,30 +807,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>encoding_time_sec</t>
+          <t>total_time_sec</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>solving_time_sec</t>
+          <t>peak_memory_mb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total_time_sec</t>
+          <t>total_clauses</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>peak_memory_mb</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>total_clauses</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>total_variables</t>
         </is>
@@ -931,19 +845,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0202972</v>
+        <v>0.0254761</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00517888</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.0254761</v>
-      </c>
-      <c r="I2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -964,19 +872,13 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0199553</v>
+        <v>0.0250924</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00513706</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.0250924</v>
-      </c>
-      <c r="I3" t="n">
         <v>8.6</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,19 +899,13 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0203587</v>
+        <v>0.0254285</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00506974</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0254285</v>
-      </c>
-      <c r="I4" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1030,19 +926,13 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0196807</v>
+        <v>0.0245407</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00486002</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0245407</v>
-      </c>
-      <c r="I5" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1063,19 +953,13 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0198155</v>
+        <v>0.0246054</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00478992</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.0246054</v>
-      </c>
-      <c r="I6" t="n">
         <v>8.6</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1096,19 +980,13 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0194543</v>
+        <v>0.0242385</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00478416</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.0242385</v>
-      </c>
-      <c r="I7" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1129,19 +1007,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0195151</v>
+        <v>0.0244289</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00491374</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.0244289</v>
-      </c>
-      <c r="I8" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1162,19 +1034,13 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0200908</v>
+        <v>0.0250318</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004941</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0250318</v>
-      </c>
-      <c r="I9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1195,19 +1061,13 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0200334</v>
+        <v>0.0249459</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00491252</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.0249459</v>
-      </c>
-      <c r="I10" t="n">
         <v>8.6</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1228,19 +1088,13 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0200459</v>
+        <v>0.0250648</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00501891</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.0250648</v>
-      </c>
-      <c r="I11" t="n">
         <v>8.6</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1263,19 +1117,13 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01992469</v>
+        <v>0.0248853</v>
       </c>
       <c r="G12" t="n">
-        <v>0.004960595</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.0248853</v>
-      </c>
-      <c r="I12" t="n">
         <v>8.569999999999999</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1288,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1319,30 +1167,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>encoding_time_sec</t>
+          <t>total_time_sec</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>solving_time_sec</t>
+          <t>peak_memory_mb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total_time_sec</t>
+          <t>total_clauses</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>peak_memory_mb</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>total_clauses</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>total_variables</t>
         </is>
@@ -1367,19 +1205,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0276765</v>
+        <v>0.0327902</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00511364</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.0327902</v>
-      </c>
-      <c r="I2" t="n">
         <v>11.5</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1400,19 +1232,13 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0273391</v>
+        <v>0.0324856</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00514643</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.0324856</v>
-      </c>
-      <c r="I3" t="n">
         <v>11.5</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1433,19 +1259,13 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0275934</v>
+        <v>0.0326968</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00510339</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0326968</v>
-      </c>
-      <c r="I4" t="n">
         <v>11.4</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1466,19 +1286,13 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0281174</v>
+        <v>0.0333142</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00519673</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0333142</v>
-      </c>
-      <c r="I5" t="n">
         <v>11.5</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1499,19 +1313,13 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0275159</v>
+        <v>0.0325547</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00503877</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.0325547</v>
-      </c>
-      <c r="I6" t="n">
         <v>11.5</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1532,19 +1340,13 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0282104</v>
+        <v>0.0334531</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00524271</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.0334531</v>
-      </c>
-      <c r="I7" t="n">
         <v>11.4</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1565,19 +1367,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0273908</v>
+        <v>0.032479</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00508815</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.032479</v>
-      </c>
-      <c r="I8" t="n">
         <v>11.4</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1598,19 +1394,13 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0278732</v>
+        <v>0.0331371</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00526387</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0331371</v>
-      </c>
-      <c r="I9" t="n">
         <v>11.6</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1631,19 +1421,13 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0275159</v>
+        <v>0.0325785</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00506259</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.0325785</v>
-      </c>
-      <c r="I10" t="n">
         <v>11.5</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1664,19 +1448,13 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0275894</v>
+        <v>0.0326558</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00506641</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.0326558</v>
-      </c>
-      <c r="I11" t="n">
         <v>11.6</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1699,19 +1477,13 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0276822</v>
+        <v>0.0328145</v>
       </c>
       <c r="G12" t="n">
-        <v>0.005132269</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.0328145</v>
-      </c>
-      <c r="I12" t="n">
         <v>11.49</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1724,7 +1496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1755,30 +1527,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>encoding_time_sec</t>
+          <t>total_time_sec</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>solving_time_sec</t>
+          <t>peak_memory_mb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total_time_sec</t>
+          <t>total_clauses</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>peak_memory_mb</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>total_clauses</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>total_variables</t>
         </is>
@@ -1803,19 +1565,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.036243</v>
+        <v>0.0415225</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00527944</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.0415225</v>
-      </c>
-      <c r="I2" t="n">
         <v>13.4</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1836,19 +1592,13 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0368803</v>
+        <v>0.0423199</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00543953</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.0423199</v>
-      </c>
-      <c r="I3" t="n">
         <v>13.3</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1869,19 +1619,13 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0362934</v>
+        <v>0.0421022</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00580882</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0421022</v>
-      </c>
-      <c r="I4" t="n">
         <v>13.3</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1902,19 +1646,13 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0367109</v>
+        <v>0.0420769</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00536601</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0420769</v>
-      </c>
-      <c r="I5" t="n">
         <v>13.4</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1935,19 +1673,13 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0376996</v>
+        <v>0.0436024</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00590281</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.0436024</v>
-      </c>
-      <c r="I6" t="n">
         <v>13.4</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1968,19 +1700,13 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0367168</v>
+        <v>0.0425617</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00584487</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.0425617</v>
-      </c>
-      <c r="I7" t="n">
         <v>13.3</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2001,19 +1727,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0372151</v>
+        <v>0.043568</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00635291</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.043568</v>
-      </c>
-      <c r="I8" t="n">
         <v>13.3</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2034,19 +1754,13 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.036205</v>
+        <v>0.0417468</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00554181</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0417468</v>
-      </c>
-      <c r="I9" t="n">
         <v>13.3</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2067,19 +1781,13 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0367507</v>
+        <v>0.0424085</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00565785</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.0424085</v>
-      </c>
-      <c r="I10" t="n">
         <v>13.4</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2100,19 +1808,13 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0362606</v>
+        <v>0.0416299</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00536924</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.0416299</v>
-      </c>
-      <c r="I11" t="n">
         <v>13.4</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2135,19 +1837,13 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03669753999999999</v>
+        <v>0.04235388</v>
       </c>
       <c r="G12" t="n">
-        <v>0.005656329</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.04235388</v>
-      </c>
-      <c r="I12" t="n">
         <v>13.35</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
